--- a/results_tables/TABLE_6.xlsx
+++ b/results_tables/TABLE_6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -499,11 +499,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[CREB1=1, TRIP13=0] (x4); [CREB1=1, CTSD=0, TRIP13=0] (x1)</t>
+          <t>[CREB1=1, TRIP13=0] (x3)</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>228.8</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -535,11 +535,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[DAXX=1, TK1=1] (x1); [CDKN1A=0, HSPB1=0, IKBKG=1] (x1)</t>
+          <t>[CDKN1A=0, DAXX=1, STAT1=1] (x1)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>177.7</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -571,30 +571,30 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[DAXX=1] (x1); [TP53=1] (x1); [PPARD=1] (x1); [ETS1=1] (x1)</t>
+          <t>[DAXX=1] (x2); [TP53=1] (x1)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>246.7</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GSM1588979</t>
+          <t>GSM1588976</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CREB1=1; CDKN1A=0</t>
+          <t>TGFB1=1; IRF2BP2=1; IKBKG=1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -607,30 +607,30 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[BCL11A=1, CREB1=1] (x2); [BCL11A=1, GABPA=1] (x1); [BCL11A=1, UBE2D1=1] (x1)</t>
+          <t>[CSNK2B=0, IRF2BP2=1] (x1); [IRF2BP2=1, TGFBR2=1] (x1); [FOS=1, HMGCR=1, IRF2BP2=1] (x1)</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>181</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GSM1588984</t>
+          <t>GSM1588977</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CREB1=1; CDKN1A=0; TRIP13=0</t>
+          <t>SQSTM1=1; DAXX=1; STAT5A=0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -643,66 +643,66 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[CDKN1A=0, TGFB1=1, TRIP13=0] (x2); [CDKN1A=0, NFE2L2=1, TRIP13=0] (x1); [CDKN1A=0, FOS=1, TRIP13=0] (x2)</t>
+          <t>[CREB1=1, HSP90AB1=0, RXRA=1] (x1); [CREB1=1, RXRA=1, STAT5A=0] (x1); [HSP90AB1=0, SQSTM1=1, TGFB1=1] (x1)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>174.1</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GSM1588995</t>
+          <t>GSM1588979</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IKBKG=1; CDKN1A=0</t>
+          <t>CREB1=1; CDKN1A=0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25/26</t>
+          <t>23/26</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[BCL11A=1, BRCA1=1] (x1); [FOS=1, TK1=1] (x1); [CDKN1A=0, DAXX=1] (x1); [BRCA1=1, CDKN1A=0] (x1); [CDKN1A=0, TGFB1=1] (x1)</t>
+          <t>[BCL11A=1, CREB1=1] (x1); [BCL11A=1, CREB1=1, UBQLN1=0] (x1); [BCL11A=1, HDAC1=0] (x1)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>169.8</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GSM1589009</t>
+          <t>GSM1588980</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ATF2=1; PARP1=1; CDKN1A=0; TRIP13=0</t>
+          <t>CREB1=1; RXRA=1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -715,30 +715,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[E2F1=1, RB1=1, TRIP13=0] (x1); [BCL11A=1, FOS=1, TRIP13=0] (x1); [RB1=0, TGFB1=1, TRIP13=0] (x1); [E2F1=1, IKBKG=1, TRIP13=0] (x2)</t>
+          <t>[CREB1=1, IKBKG=1, RXRA=1, STAT1=1, TRIP13=0] (x1); [BCL6=0, CD44=0, CREB1=1, RXRA=1, TRIP13=0] (x1); [RXRA=1, STAT1=1, TGFBR2=1, TRIP13=0] (x1)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>174.4</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GSM1589016</t>
+          <t>GSM1588982</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TK1=1; FOS=1</t>
+          <t>CREB1=1; RXRA=1; TRIP13=0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -751,30 +751,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[FOS=1, IRF2BP2=1] (x1); [CDKN1A=0, TGFB1=1] (x1); [IKBKG=1, TK1=1] (x1); [CDKN1A=0, IKBKG=1] (x1)</t>
+          <t>[CREB1=1, RXRA=1, SERPINA3=1, TRIP13=0] (x1); [IKBKG=1, RXRA=1, SMAD3=1, TRIP13=0] (x1); [BTG3=1, DAXX=1, RXRA=1, TRIP13=0] (x1)</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>268.7</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GSM1589031</t>
+          <t>GSM1588984</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SETDB1=1; TRIP13=0</t>
+          <t>CREB1=1; CDKN1A=0; TRIP13=0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -787,30 +787,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[RXRA=1, TRIP13=0] (x2); [TGFB1=1, TRIP13=0] (x1); [FOS=1, TRIP13=0] (x1); [BCL6=0, TRIP13=0] (x1)</t>
+          <t>[CDKN1A=0, TGFBR2=1, TRIP13=0] (x2)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>164.5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GSM1589039</t>
+          <t>GSM1588985</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TRIB3=1; IKBKG=1; RXRA=1</t>
+          <t>TGFB1=1; PPARD=0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -823,83 +823,515 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[RB1=0, RXRA=1] (x1); [MTA1=1, RXRA=1] (x2); [EZH2=1, RXRA=1] (x1); [FOS=1, RXRA=1, TP53=0] (x1)</t>
+          <t>[FOS=1, PML=0, PPARG=0] (x1); [FOS=1, PPARD=0] (x1); [FOS=1, TRIB3=0, USP7=1] (x1)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>186.5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GSM1589045</t>
+          <t>GSM1588986</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IRF2BP2=1; BRCA1=1</t>
+          <t>BRCA1=1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25/26</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[BCL11A=1, FOS=1] (x1); [BRCA1=1, CDKN1A=0] (x2); [BRCA1=1, TK1=1] (x2)</t>
+          <t>[SETDB1=1] (x1)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>174.9</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GSM1588988</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HIF1A=0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25/26</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[VIM=1] (x1); [CDC20=0] (x1); [YWHAB=0] (x1)</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GSM1588993</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MAP3K4=0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[VIM=1] (x1); [CDC20=0] (x1); [YWHAB=0] (x1)</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>81.59999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GSM1588995</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IKBKG=1; CDKN1A=0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25/26</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>25</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[BRCA1=1, TK1=1] (x1); [E2F1=1, TRIB3=1] (x1); [BCL11A=1, FOS=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>99.09999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GSM1589009</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ATF2=1; PARP1=1; CDKN1A=0; TRIP13=0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[IRF2BP2=1, RB1=1, TRIP13=0] (x1); [CD82=1, FOS=1, RELA=1, TRIP13=0] (x1); [GABPA=1, IRF2BP2=1, TRIP13=0] (x1)</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GSM1589012</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RELA=1; RXRA=1; ACTB=0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[HDAC1=1, RXRA=1, TGFB1=1] (x1); [BCL11A=1, MTA1=0, RXRA=1, SMAD3=0] (x1); [CSNK2B=1, RELA=1, RXRA=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>151.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GSM1589016</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TK1=1; FOS=1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[FOS=1, IRF2BP2=1] (x1); [IKBKG=1, TK1=1] (x1); [CDKN1A=0, IKBKG=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>154.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GSM1589024</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TK1=1; TGFBR2=1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>25/26</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[BCL11A=1, TGFBR2=1] (x1); [CDKN1A=0, TGFB1=1] (x1); [BCL11A=1, FOS=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>116.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>26</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GSM1589031</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SETDB1=1; TRIP13=0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>23</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[TGFBR2=1, TRIP13=0] (x1); [FOS=1, PPARD=1, TRIP13=0] (x1); [BRCA1=1, TRIP13=0] (x1)</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GSM1589037</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FOS=1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>23</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[HDAC1=0] (x1); [DAXX=1] (x1); [TGFB1=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GSM1589039</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TRIB3=1; IKBKG=1; RXRA=1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25/26</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[RB1=0, RXRA=1] (x1); [MTA1=1, RXRA=1] (x1); [BRCA1=1, NFKB1=1, RXRA=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>34</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GSM1589045</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IRF2BP2=1; BRCA1=1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>25/26</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[BRCA1=1, CDKN1A=0] (x2); [BRCA1=1, IRF2BP2=1, PARP1=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>102.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>37</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GSM1589058</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CDKN1A=0; TRIP13=0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>23</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>None observed</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>86.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>39</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>GSM1589061</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>RXRA=1; STAT3=1; TM4SF1=0; FOS=1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0/5</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>23/26</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[ACTB=0, FOS=1, RXRA=1] (x1); [BCL6=0, IKBKG=1, RXRA=1] (x1); [IKBKG=1, NFE2L2=1, RXRA=1] (x1); [RXRA=1, STAT1=1, TGFBR2=1] (x1); [CCND1=1, FOS=1, RXRA=1] (x1)</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>189.9</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[PPARD=0, RXRA=1, TGFB1=1] (x1); [RXRA=1, TGFB1=1, USP7=1] (x1); [RXRA=1, SQSTM1=1, TGFBR2=1, TNRC6A=1] (x1)</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>116.3</v>
       </c>
     </row>
   </sheetData>
